--- a/AAAGameData/DataTables/ChessAdvanceTable.xlsx
+++ b/AAAGameData/DataTables/ChessAdvanceTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
   <si>
     <t>#</t>
   </si>
@@ -38,12 +38,6 @@
     <t>Id</t>
   </si>
   <si>
-    <t>Rank</t>
-  </si>
-  <si>
-    <t>AdvancedChessId</t>
-  </si>
-  <si>
     <t>RequiredEXP</t>
   </si>
   <si>
@@ -56,25 +50,28 @@
     <t>int</t>
   </si>
   <si>
-    <t>棋子ID（等于进阶前棋子ID，直接按棋子ID查询）</t>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>棋子ID</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
-    <t>当前阶级（1=一阶）</t>
-  </si>
-  <si>
-    <t>进阶后棋子ID（0=已是最高阶）</t>
-  </si>
-  <si>
-    <t>进阶所需经验值（0=无法进阶）</t>
-  </si>
-  <si>
-    <t>进阶条件事件ID（0=无附加条件，后续接事件系统）</t>
-  </si>
-  <si>
-    <t>进阶特效资源ID（0=无特效）</t>
+    <t>升阶所需经验值数组（1升2, 2升3）</t>
+  </si>
+  <si>
+    <t>升阶条件事件ID数组（1升2, 2升3）</t>
+  </si>
+  <si>
+    <t>升阶特效资源ID</t>
+  </si>
+  <si>
+    <t>10,20</t>
+  </si>
+  <si>
+    <t>0,0</t>
   </si>
 </sst>
 </file>
@@ -688,13 +685,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1043,19 +1043,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="4" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1063,13 +1061,11 @@
         <v>1</v>
       </c>
       <c r="C1" s="3"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1077,167 +1073,119 @@
         <v>2</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>8</v>
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:8">
+    <row r="5" ht="15" customHeight="1" spans="1:6">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1002</v>
-      </c>
-      <c r="F5" s="3">
-        <v>500</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2">
         <v>0</v>
       </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:8">
+    <row r="6" ht="15" customHeight="1" spans="1:6">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
-        <v>1002</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3">
-        <v>2</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1003</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G6" s="3">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="2">
         <v>0</v>
       </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:8">
+    <row r="7" ht="15" customHeight="1" spans="1:6">
       <c r="A7" s="2"/>
-      <c r="B7" s="2">
-        <v>1003</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
+      <c r="B7" s="2"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:8">
-      <c r="C8" s="3"/>
+    <row r="8" ht="15" customHeight="1" spans="1:6">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:8">
-      <c r="C9" s="3"/>
+    <row r="9" ht="15" customHeight="1" spans="1:6">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:8">
-      <c r="C10" s="3"/>
+    <row r="10" ht="15" customHeight="1" spans="1:6">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:8">
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" s="3"/>
+    <row r="11" ht="15" customHeight="1" spans="1:6">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/ChessAdvanceTable.xlsx
+++ b/AAAGameData/DataTables/ChessAdvanceTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
   <si>
     <t>#</t>
   </si>
@@ -68,7 +68,7 @@
     <t>升阶特效资源ID</t>
   </si>
   <si>
-    <t>10,20</t>
+    <t>85,150</t>
   </si>
   <si>
     <t>0,0</t>
@@ -84,7 +84,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -540,158 +547,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1043,149 +1046,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="8" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="34" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="2"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:6">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:6">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="C6" s="1"/>
+      <c r="D6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:6">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:6">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="2"/>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:6">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:6">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:6">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="2"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
